--- a/经济性分析测试模板（不含蒸汽）_optimized_result.xlsx
+++ b/经济性分析测试模板（不含蒸汽）_optimized_result.xlsx
@@ -1,41 +1,523 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="24750" windowHeight="11630"/>
   </bookViews>
   <sheets>
-    <sheet name="dispatch_result" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="dispatch_result" sheetId="1" r:id="rId1"/>
+    <sheet name="summary" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+  <si>
+    <t>时间</t>
+  </si>
+  <si>
+    <t>需冷量_kw</t>
+  </si>
+  <si>
+    <t>电价</t>
+  </si>
+  <si>
+    <t>冷机制冷量_kw</t>
+  </si>
+  <si>
+    <t>蓄冷放冷量_kw</t>
+  </si>
+  <si>
+    <t>冷机负载率_%</t>
+  </si>
+  <si>
+    <t>小时总耗电_kWh</t>
+  </si>
+  <si>
+    <t>小时电费</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
+    <t>03:00:00</t>
+  </si>
+  <si>
+    <t>04:00:00</t>
+  </si>
+  <si>
+    <t>05:00:00</t>
+  </si>
+  <si>
+    <t>06:00:00</t>
+  </si>
+  <si>
+    <t>07:00:00</t>
+  </si>
+  <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>09:00:00</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
+    <t>指标</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>求解状态</t>
+  </si>
+  <si>
+    <t>Optimal</t>
+  </si>
+  <si>
+    <t>当日最大耗电_kW</t>
+  </si>
+  <si>
+    <t>总电费</t>
+  </si>
+  <si>
+    <t>总耗电_kWh</t>
+  </si>
+  <si>
+    <t>其中能量电费</t>
+  </si>
+  <si>
+    <t>其中需量电费</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -43,85 +525,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -404,822 +1113,744 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <cols>
+    <col min="4" max="4" width="15.9090909090909" customWidth="1"/>
+    <col min="5" max="5" width="14.9090909090909" customWidth="1"/>
+    <col min="6" max="6" width="16.2727272727273" customWidth="1"/>
+    <col min="7" max="7" width="14.7272727272727" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>需冷量_kw</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>电价</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>冷机制冷量_kw</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>蓄冷放冷量_kw</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>冷机负载率_%</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>小时总耗电_kWh</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>小时电费</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>00:00:00</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
         <v>6759.02</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0.2203</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>6759.02</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>96.11803185437998</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2">
+        <v>96.11803185438</v>
+      </c>
+      <c r="G2">
         <v>1307.5328</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>301.8748136</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>01:00:00</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
         <v>6833.49</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>0.2203</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>6833.49</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
-        <v>97.17704778156997</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="F3">
+        <v>97.17704778157</v>
+      </c>
+      <c r="G3">
         <v>1324.504</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>305.61356896</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>02:00:00</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
         <v>6756.07</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0.2203</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>6756.07</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
-        <v>96.07608077360636</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F4">
+        <v>96.0760807736064</v>
+      </c>
+      <c r="G4">
         <v>1306.8605</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>301.72670591</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>03:00:00</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
         <v>6761.13</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>0.2203</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>6761.13</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
-        <v>96.14803754266211</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F5">
+        <v>96.1480375426621</v>
+      </c>
+      <c r="G5">
         <v>1308.0136</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>301.98073384</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>04:00:00</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
         <v>6735.04</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>0.2203</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>6735.04</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
-        <v>95.77701934015927</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6">
+        <v>95.7770193401593</v>
+      </c>
+      <c r="G6">
         <v>1302.0678</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>300.6708741</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>05:00:00</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
         <v>6782.21</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>0.2203</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>6782.21</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
-        <v>96.44781001137656</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="F7">
+        <v>96.4478100113766</v>
+      </c>
+      <c r="G7">
         <v>1312.8176</v>
       </c>
-      <c r="H7" t="n">
-        <v>303.0390550400001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>06:00:00</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="H7">
+        <v>303.03905504</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
         <v>6736.83</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>0.2203</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>6736.83</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
-        <v>95.80247440273038</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="F8">
+        <v>95.8024744027304</v>
+      </c>
+      <c r="G8">
         <v>1302.4758</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>300.7607565</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>07:00:00</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9">
         <v>6907.68</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>0.2203</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>6907.68</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>98.2320819112628</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1341.4115</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>309.33829121</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10">
         <v>7278.19</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>0.9564</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>7032</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>246.19</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>100</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1427.807</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>1379.37995256</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11">
         <v>8062.28</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>1.1477</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>7032</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>1030.28</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>100</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>1612.7339</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>1864.76003479</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
         <v>8739.6</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>1.1477</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>7032</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>1707.6</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>100</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>1772.4792</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>2048.0997156</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>8618.549999999999</v>
-      </c>
-      <c r="C13" t="n">
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <v>8618.55</v>
+      </c>
+      <c r="C13">
         <v>0.2203</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>7032</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>1586.55</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>100</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>1743.9296</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>398.01302864</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>8602.049999999999</v>
-      </c>
-      <c r="C14" t="n">
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14">
+        <v>8602.05</v>
+      </c>
+      <c r="C14">
         <v>0.2203</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>7032</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>1570.05</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>100</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>1740.0381</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>397.15573119</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>13:00:00</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>8499.879999999999</v>
-      </c>
-      <c r="C15" t="n">
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15">
+        <v>8499.88</v>
+      </c>
+      <c r="C15">
         <v>0.5796</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>7032</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>1467.88</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>100</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>1715.9414</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>1008.3849732</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16">
         <v>8447.85</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>0.5796</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>7032</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>1415.85</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>100</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>1703.6702</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>1001.27258568</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>15:00:00</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17">
         <v>7561.75</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>1.1477</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>7032</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>529.75</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>100</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>1494.6844</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>1729.27462364</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18">
         <v>7335.91</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>1.1477</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>7032</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>303.91</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>100</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>1441.4202</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>1668.1433013</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19">
         <v>7369.5</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>0.9564</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>7032</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>337.5</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>100</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>1449.3424</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>1399.97640912</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20">
         <v>7425.73</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>0.9564</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>7032</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>393.73</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>100</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>1462.6042</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>1412.65999464</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21">
         <v>7146.04</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>0.9564</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>7032</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>114.04</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>100</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>1396.6396</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>1349.5714512</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22">
         <v>7373.37</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>0.9564</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>7032</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>341.37</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>100</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>1450.2551</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>1400.8493154</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23">
         <v>7078.45</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>0.9564</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>7032</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>46.45</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>100</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>1380.6985</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>1334.32538316</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24">
         <v>7373.73</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>0.9564</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>7032</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>341.73</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>100</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>1450.34</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>1400.93051376</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25">
         <v>7136.02</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>0.5796</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>7032</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>104.02</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>100</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>1394.2763</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>821.94788124</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>指标</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>求解状态</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>当日最大耗电_kW</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3">
         <v>1772.4792</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>总电费</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4">
         <v>23039.74969428</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>总耗电_kWh</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>35142.54369999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>其中能量电费</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5">
+        <v>35142.5437</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6">
         <v>22707.94158804</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>其中需量电费</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7">
         <v>331.80810624</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>